--- a/VALIDA (1).xlsx
+++ b/VALIDA (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beca\OneDrive\Escritorio\LOLIUM 2026\valida AZUL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32C6511-80B4-4B2B-81F8-6AFC3F3A2872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B04149-A6A6-4354-BF48-85CE3973C404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -431,14 +431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,15 +446,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B2" s="5">
         <v>2713</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46119</v>
       </c>
@@ -462,86 +462,104 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="7"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B6" s="4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="4">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="4"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="4"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="4"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="4"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
     </row>
